--- a/data/trans_dic/P25D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Edad-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 6,78</t>
+          <t>0,72; 6,9</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,49</t>
+          <t>0,0; 4,24</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,77; 4,55</t>
+          <t>0,81; 4,52</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,29</t>
+          <t>0,35; 3,11</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,89</t>
+          <t>0,41; 2,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,55; 2,36</t>
+          <t>0,61; 2,39</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,92; 3,6</t>
+          <t>0,97; 3,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,76</t>
+          <t>0,34; 1,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,8; 2,4</t>
+          <t>0,77; 2,26</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,06; 1,05</t>
+          <t>0,07; 1,04</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,49</t>
+          <t>0,38; 1,42</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,26; 1,01</t>
+          <t>0,29; 0,98</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,47; 2,29</t>
+          <t>0,49; 2,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,99</t>
+          <t>0,08; 0,79</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,37; 1,31</t>
+          <t>0,39; 1,39</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,54</t>
+          <t>0,0; 0,98</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,64</t>
+          <t>0,0; 0,72</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,05; 0,62</t>
+          <t>0,0; 0,6</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0; 0,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,45</t>
+          <t>0,0; 0,41</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,27</t>
+          <t>0,0; 0,31</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,69; 1,66</t>
+          <t>0,68; 1,68</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,97</t>
+          <t>0,42; 0,99</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,16</t>
+          <t>0,62; 1,15</t>
         </is>
       </c>
     </row>
@@ -978,7 +978,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que fuma diariamente cigarrillos electrónicos</t>
+          <t>Población que fuma diariamente cigarrillos electrónicos (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3229; 27103</t>
+          <t>2876; 27584</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 14048</t>
+          <t>0; 13279</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5498; 32485</t>
+          <t>5743; 32241</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1602; 13901</t>
+          <t>1476; 13142</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2119; 14758</t>
+          <t>2123; 14899</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5106; 21997</t>
+          <t>5723; 22285</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>4922; 19311</t>
+          <t>5202; 19786</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1759; 9513</t>
+          <t>1860; 9214</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8637; 25864</t>
+          <t>8288; 24378</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>535; 9250</t>
+          <t>578; 9151</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2762; 10633</t>
+          <t>2725; 10138</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4164; 16050</t>
+          <t>4695; 15687</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2647; 12816</t>
+          <t>2727; 13279</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>442; 5428</t>
+          <t>442; 4328</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4061; 14500</t>
+          <t>4302; 15321</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 5654</t>
+          <t>0; 3610</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 3867</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>456; 6042</t>
+          <t>0; 5883</t>
         </is>
       </c>
     </row>
@@ -1521,17 +1521,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>0; 1183</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1897</t>
+          <t>0; 1731</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 1907</t>
+          <t>0; 2162</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23831; 57128</t>
+          <t>23553; 57918</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15475; 35432</t>
+          <t>15300; 36286</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44527; 82700</t>
+          <t>44134; 81536</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25D_R-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P25D_R-Edad-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,61%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,24%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,72; 6,9</t>
+          <t>1,14; 7,75</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 4,24</t>
+          <t>0,0; 4,21</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,52</t>
+          <t>0,94; 4,47</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,31%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,35; 3,11</t>
+          <t>0,34; 3,21</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,91</t>
+          <t>0,49; 3,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,61; 2,39</t>
+          <t>0,64; 2,35</t>
         </is>
       </c>
     </row>
@@ -649,12 +649,12 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,69</t>
+          <t>0,97; 3,6</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,34; 1,71</t>
+          <t>0,36; 1,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,77; 2,26</t>
+          <t>0,8; 2,19</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,04</t>
+          <t>0,16; 1,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,38; 1,42</t>
+          <t>0,47; 1,63</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0,29; 0,98</t>
+          <t>0,35; 1,14</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,49; 2,37</t>
+          <t>0,46; 2,13</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,08; 0,79</t>
+          <t>0,08; 0,82</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,39; 1,39</t>
+          <t>0,33; 1,25</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,28%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,98</t>
+          <t>0,0; 1,3</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,72</t>
+          <t>0,0; 1,03</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,6</t>
+          <t>0,07; 0,87</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,08%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -877,12 +877,12 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,41</t>
+          <t>0,0; 0,5</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,0; 0,31</t>
+          <t>0,0; 0,25</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>0,68; 1,68</t>
+          <t>0,81; 1,77</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0,42; 0,99</t>
+          <t>0,48; 1,05</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0,62; 1,15</t>
+          <t>0,7; 1,27</t>
         </is>
       </c>
     </row>
@@ -1060,17 +1060,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>10458</t>
+          <t>13326</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>4020</t>
+          <t>3966</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14478</t>
+          <t>17292</t>
         </is>
       </c>
     </row>
@@ -1083,17 +1083,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2876; 27584</t>
+          <t>4632; 31607</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 13279</t>
+          <t>0; 15263</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>5743; 32241</t>
+          <t>7212; 34405</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>5808</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>6189</t>
+          <t>6626</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11716</t>
+          <t>12434</t>
         </is>
       </c>
     </row>
@@ -1156,17 +1156,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1476; 13142</t>
+          <t>1598; 15279</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>2123; 14899</t>
+          <t>2477; 15312</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5723; 22285</t>
+          <t>6214; 22926</t>
         </is>
       </c>
     </row>
@@ -1206,17 +1206,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>10707</t>
+          <t>12124</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>4382</t>
+          <t>5284</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15088</t>
+          <t>17408</t>
         </is>
       </c>
     </row>
@@ -1229,17 +1229,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5202; 19786</t>
+          <t>6039; 22290</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1860; 9214</t>
+          <t>2259; 10032</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8288; 24378</t>
+          <t>9957; 27169</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1279,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>3230</t>
+          <t>3488</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5965</t>
+          <t>6627</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>9195</t>
+          <t>10115</t>
         </is>
       </c>
     </row>
@@ -1302,17 +1302,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>578; 9151</t>
+          <t>1128; 9347</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2725; 10138</t>
+          <t>3476; 12011</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>4695; 15687</t>
+          <t>4991; 16348</t>
         </is>
       </c>
     </row>
@@ -1352,17 +1352,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>6626</t>
+          <t>6806</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1661</t>
+          <t>1766</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>8287</t>
+          <t>8571</t>
         </is>
       </c>
     </row>
@@ -1375,17 +1375,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>2727; 13279</t>
+          <t>2776; 12931</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>442; 4328</t>
+          <t>476; 4959</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4302; 15321</t>
+          <t>4007; 15193</t>
         </is>
       </c>
     </row>
@@ -1425,17 +1425,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>864</t>
+          <t>1053</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>1146</t>
+          <t>1285</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2338</t>
         </is>
       </c>
     </row>
@@ -1448,17 +1448,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>0; 3610</t>
+          <t>0; 5272</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 4537</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5883</t>
+          <t>623; 7342</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>377</t>
+          <t>390</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>0; 1731</t>
+          <t>0; 2341</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>0; 2162</t>
+          <t>0; 1969</t>
         </is>
       </c>
     </row>
@@ -1571,17 +1571,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>37411</t>
+          <t>42606</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>23740</t>
+          <t>25944</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>68550</t>
         </is>
       </c>
     </row>
@@ -1594,17 +1594,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>23553; 57918</t>
+          <t>28507; 62490</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>15300; 36286</t>
+          <t>17746; 39041</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>44134; 81536</t>
+          <t>50758; 92172</t>
         </is>
       </c>
     </row>
